--- a/data/ground_truth/PTBA.xlsx
+++ b/data/ground_truth/PTBA.xlsx
@@ -431,7 +431,7 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>AADI</t>
+          <t>PTBA</t>
         </is>
       </c>
       <c r="E1" s="2" t="n"/>
